--- a/stories/arbres/ATOM-SAN.SOM.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Quentin sort du bain. L'eau chaude sent le savon doux. Maman tend le pyjama bleu. Quentin glisse les bras. Le pyjama est moelleux. Papa dit : le corps a besoin de dormir. Quentin va dans la chambre. Il se couche. Papa raconte une petite histoire. Quentin pose la tête. L'oreiller est frais. Maman baisse la lumière. C'est l'heure du dodo. Quentin ferme les yeux. Le soir, pyjama, puis dodo.</t>
+          <t>Le soir, Quentin sort du bain. L'eau chaude sent le savon doux. Maman tend le pyjama bleu. Quentin glisse les bras. Le pyjama est moelleux. Le corps a besoin de dormir. Quentin va dans la chambre. Il se couche. Papa raconte une petite histoire. Quentin pose la tête. L'oreiller est frais. Maman baisse la lumière. C'est l'heure du dodo. Quentin ferme les yeux. Le soir, pyjama, puis dodo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Quentin sort du bain. L'eau chaude sent le savon doux. Maman tend le pyjama bleu. Quentin glisse les bras. Le pyjama est moelleux.
+papa|Le corps a besoin de dormir.
+narrateur|Quentin va dans la chambre. Il se couche. Papa raconte une petite histoire. Quentin pose la tête. L'oreiller est frais. Maman baisse la lumière. C'est l'heure du dodo. Quentin ferme les yeux. Le soir, pyjama, puis dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Quentin va dormir. Que met-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Quentin a mis le pyjama. Il s'est couché. Le soir, c'est le dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1824,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Quentin respire doucement. Papa reste un moment.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1991,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Quentin va dans la chambre. Il se couche. Papa raconte une petite histoire. Quentin pose la tête. L'oreiller est frais. Maman baisse la lumière. C'est l'heure du dodo. Quentin ferme les yeux. Le soir, pyjama, puis dodo.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Quentin va dormir. Que met-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Quentin a mis le pyjama. Il s'est couché. Le soir, c'est le dodo.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1837,7 @@
           <t>narrateur|Quentin respire doucement. Papa reste un moment.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2048,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2263,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.SOM.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quentin met le pyjama</t>
+          <t>Le nuage sur le miroir</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.003</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un nuage de buée s'étire sur le miroir. Nino sort du bain. Maman tend le pyjama bleu. Papa ouvre le lit. Nino se couche. Soir, pyjama, dodo.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Quentin sort du bain. L'eau chaude sent le savon doux. Maman tend le pyjama bleu. Quentin glisse les bras. Le pyjama est moelleux. Le corps a besoin de dormir. Quentin va dans la chambre. Il se couche. Papa raconte une petite histoire. Quentin pose la tête. L'oreiller est frais. Maman baisse la lumière. C'est l'heure du dodo. Quentin ferme les yeux. Le soir, pyjama, puis dodo.</t>
+          <t>La buée dessine un nuage sur le miroir. La salle de bain sent le savon. Une goutte glisse le long du carreau. Elle fait une petite route brillante. Le tapis de bain est chaud sous les pieds. Dehors, le village s'est calmé. Les volets sont fermés, tout doux. Nino vit ici, avec papa et maman. En ce moment, l'eau du bain est encore tiède. Tu as fini le bain, Nino ? Oui, maman. L'eau est douce. Viens. Le pyjama t'attend. Maman tend une serviette épaisse. La serviette sent le linge chaud. Nino se sèche près du tapis. Bravo. Tu es bien au sec. Le pyjama bleu attend sur la chaise. Il est moelleux, tout plié. Il est doux, maman. Oui. Glisse les bras. Nino glisse un bras, puis l'autre. Les manches sont chaudes. Il boutonne le devant, tout seul. Bravo, Nino. Tu as mis le pyjama. Le soir, on met le pyjama. Puis le dodo ? Puis le dodo. Viens dans la chambre. Le couloir est un peu sombre. Une petite lampe veille au bout. Papa ouvre le lit. L'oreiller est frais, bien blanc. Viens te coucher, Nino. Le corps a besoin de dormir. Nino pose la tête. La couverture sent le propre. Tu veux une petite histoire ? Oui, papa. Une toute courte. Papa raconte un petit bateau. Le bateau glisse sur l'eau calme. Il va où, le bateau ? Vers la rive. Tout doucement. Nino écoute. Ses yeux deviennent lourds. Je baisse la lumière. C'est l'heure du dodo. Ce n'est pas une punition. C'est le dodo. Le soir, on se couche. Pyjama, puis dodo. Oui. Bravo. Tu as fait du bon travail. Nino ferme les yeux. Il respire doucement. Le nuage du miroir s'efface déjà.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1329,58 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Quentin sort du bain. L'eau chaude sent le savon doux. Maman tend le pyjama bleu. Quentin glisse les bras. Le pyjama est moelleux.
+          <t>narrateur|La buée dessine un nuage sur le miroir.
+narrateur|La salle de bain sent le savon.
+narrateur|Une goutte glisse le long du carreau.
+narrateur|Elle fait une petite route brillante.
+narrateur|Le tapis de bain est chaud sous les pieds.
+narrateur|Dehors, le village s'est calmé.
+narrateur|Les volets sont fermés, tout doux.
+narrateur|Nino vit ici, avec papa et maman.
+narrateur|En ce moment, l'eau du bain est encore tiède.
+maman|Tu as fini le bain, Nino ?
+enfant-m|Oui, maman. L'eau est douce.
+maman|Viens. Le pyjama t'attend.
+narrateur|Maman tend une serviette épaisse.
+narrateur|La serviette sent le linge chaud.
+narrateur|Nino se sèche près du tapis.
+maman|Bravo. Tu es bien au sec.
+narrateur|Le pyjama bleu attend sur la chaise.
+narrateur|Il est moelleux, tout plié.
+enfant-m|Il est doux, maman.
+maman|Oui. Glisse les bras.
+narrateur|Nino glisse un bras, puis l'autre.
+narrateur|Les manches sont chaudes.
+narrateur|Il boutonne le devant, tout seul.
+maman|Bravo, Nino. Tu as mis le pyjama.
+maman|Le soir, on met le pyjama.
+enfant-m|Puis le dodo ?
+maman|Puis le dodo. Viens dans la chambre.
+narrateur|Le couloir est un peu sombre.
+narrateur|Une petite lampe veille au bout.
+narrateur|Papa ouvre le lit.
+narrateur|L'oreiller est frais, bien blanc.
+papa|Viens te coucher, Nino.
 papa|Le corps a besoin de dormir.
-narrateur|Quentin va dans la chambre. Il se couche. Papa raconte une petite histoire. Quentin pose la tête. L'oreiller est frais. Maman baisse la lumière. C'est l'heure du dodo. Quentin ferme les yeux. Le soir, pyjama, puis dodo.</t>
+narrateur|Nino pose la tête.
+narrateur|La couverture sent le propre.
+papa|Tu veux une petite histoire ?
+enfant-m|Oui, papa. Une toute courte.
+narrateur|Papa raconte un petit bateau.
+narrateur|Le bateau glisse sur l'eau calme.
+enfant-m|Il va où, le bateau ?
+papa|Vers la rive. Tout doucement.
+narrateur|Nino écoute.
+narrateur|Ses yeux deviennent lourds.
+maman|Je baisse la lumière.
+maman|C'est l'heure du dodo.
+papa|Ce n'est pas une punition.
+papa|C'est le dodo. Le soir, on se couche.
+enfant-m|Pyjama, puis dodo.
+papa|Oui. Bravo. Tu as fait du bon travail.
+narrateur|Nino ferme les yeux.
+narrateur|Il respire doucement.
+narrateur|Le nuage du miroir s'efface déjà.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1342,7 +1408,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Quentin va dormir. Que met-il ?</t>
+          <t>Nino va dormir. Que met-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1498,7 +1564,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Quentin va dormir. Que met-il ?</t>
+          <t>narrateur|Nino va dormir.
+narrateur|Que met-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1526,7 +1593,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Quentin a mis le pyjama. Il s'est couché. Le soir, c'est le dodo.</t>
+          <t>Nino a mis le pyjama. Il s'est couché. Tu as mis le pyjama, Nino ? Oui, papa. Le bleu. Bravo. Le soir, c'est le dodo. Tu as fait du bon travail. La chambre sent encore le savon, un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,7 +1737,13 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Quentin a mis le pyjama. Il s'est couché. Le soir, c'est le dodo.</t>
+          <t>narrateur|Nino a mis le pyjama.
+narrateur|Il s'est couché.
+papa|Tu as mis le pyjama, Nino ?
+enfant-m|Oui, papa. Le bleu.
+papa|Bravo. Le soir, c'est le dodo.
+maman|Tu as fait du bon travail.
+narrateur|La chambre sent encore le savon, un peu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1698,7 +1771,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Quentin respire doucement. Papa reste un moment.</t>
+          <t>Papa pose le livre du bateau. Tu as encore soif ? Un peu d'eau. Maman tend le verre. Nino boit une gorgée. L'eau est fraîche. On reste un moment, tout calme. Nino respire. Le pyjama est chaud. La goutte sur le carreau a séché.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1834,7 +1907,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Quentin respire doucement. Papa reste un moment.</t>
+          <t>narrateur|Papa pose le livre du bateau.
+maman|Tu as encore soif ?
+enfant-m|Un peu d'eau.
+narrateur|Maman tend le verre.
+narrateur|Nino boit une gorgée.
+narrateur|L'eau est fraîche.
+papa|On reste un moment, tout calme.
+narrateur|Nino respire.
+narrateur|Le pyjama est chaud.
+narrateur|La goutte sur le carreau a séché.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1862,7 +1944,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai mis le pyjama. On a fait le dodo. Bravo, Nino. Le soir, pyjama, puis dodo. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2002,7 +2084,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai mis le pyjama.
+enfant-m|On a fait le dodo.
+papa|Bravo, Nino.
+maman|Le soir, pyjama, puis dodo.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2024,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2062,6 +2148,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-04.xlsx
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La buée dessine un nuage sur le miroir. La salle de bain sent le savon. Une goutte glisse le long du carreau. Elle fait une petite route brillante. Le tapis de bain est chaud sous les pieds. Dehors, le village s'est calmé. Les volets sont fermés, tout doux. Nino vit ici, avec papa et maman. En ce moment, l'eau du bain est encore tiède. Tu as fini le bain, Nino ? Oui, maman. L'eau est douce. Viens. Le pyjama t'attend. Maman tend une serviette épaisse. La serviette sent le linge chaud. Nino se sèche près du tapis. Bravo. Tu es bien au sec. Le pyjama bleu attend sur la chaise. Il est moelleux, tout plié. Il est doux, maman. Oui. Glisse les bras. Nino glisse un bras, puis l'autre. Les manches sont chaudes. Il boutonne le devant, tout seul. Bravo, Nino. Tu as mis le pyjama. Le soir, on met le pyjama. Puis le dodo ? Puis le dodo. Viens dans la chambre. Le couloir est un peu sombre. Une petite lampe veille au bout. Papa ouvre le lit. L'oreiller est frais, bien blanc. Viens te coucher, Nino. Le corps a besoin de dormir. Nino pose la tête. La couverture sent le propre. Tu veux une petite histoire ? Oui, papa. Une toute courte. Papa raconte un petit bateau. Le bateau glisse sur l'eau calme. Il va où, le bateau ? Vers la rive. Tout doucement. Nino écoute. Ses yeux deviennent lourds. Je baisse la lumière. C'est l'heure du dodo. Ce n'est pas une punition. C'est le dodo. Le soir, on se couche. Pyjama, puis dodo. Oui. Bravo. Tu as fait du bon travail. Nino ferme les yeux. Il respire doucement. Le nuage du miroir s'efface déjà.</t>
+          <t>La buée dessine un nuage sur le miroir. La salle de bain sent le savon. Une goutte glisse le long du carreau. Elle fait une petite route brillante. Le tapis de bain est chaud sous les pieds. Dehors, le village s'est calmé. Les volets sont fermés, tout doux. Nino vit ici, avec papa et maman. En ce moment, l'eau du bain est encore tiède. Tu as fini le bain, Nino ? Oui, maman. L'eau est douce. Viens. Le pyjama t'attend. Maman tend une serviette épaisse. La serviette sent le linge chaud. Nino se sèche près du tapis. Bravo. Tu es bien au sec. Le pyjama bleu attend sur la chaise. Il est moelleux, tout plié. Il est doux, maman. Oui. Glisse les bras. Nino glisse un bras, puis l'autre. Les manches sont chaudes. Il boutonne le devant, tout seul. Bravo, Nino. Tu as mis le pyjama. Le soir, on met le pyjama. Puis le dodo ? Puis le dodo. Viens dans la chambre. Le couloir est un peu sombre. Une petite lampe veille au bout. Papa ouvre le lit. L'oreiller est frais, bien blanc. Viens te coucher, Nino. Le corps a besoin de dormir. Nino pose la tête. La couverture sent le propre. Tu veux une petite histoire ? Oui, papa. Une toute courte. Papa raconte un petit bateau. Le bateau glisse sur l'eau calme. Il va où, le bateau ? Vers la rive. Tout doucement. Nino écoute. Ses yeux deviennent lourds. Je baisse la lumière. C'est l'heure du dodo. Ce n'est pas une punition. C'est le dodo. Le soir, on se couche. Pyjama, puis dodo. Oui. Bravo. Nino ferme les yeux. Il respire doucement. Le nuage du miroir s'efface déjà.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt;, Quentin sort du bain. L'eau chaude sent le savon doux. Maman tend le pyjama bleu. Quentin glisse les bras. Le pyjama est moelleux. Papa dit : le corps a besoin de dormir. Quentin va dans la chambre. Il se couche. Papa raconte une petite histoire. Quentin pose la tête. L'oreiller est frais. Maman baisse la lumière. C'est l'heure du dodo. Quentin ferme les yeux. Le soir, pyjama, puis dodo.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La buée dessine un nuage sur le miroir. La salle de bain sent le savon. Une goutte glisse le long du carreau. Elle fait une petite route brillante. Le tapis de bain est chaud sous les pieds. Dehors, le village s'est calmé. Les volets sont fermés, tout doux. Nino vit ici, avec papa et maman. En ce moment, l'eau du bain est encore tiède. Tu as fini le bain, Nino ? Oui, maman. L'eau est douce. Viens. Le pyjama t'attend. Maman tend une serviette épaisse. La serviette sent le linge chaud. Nino se sèche près du tapis. Bravo. Tu es bien au sec. Le pyjama bleu attend sur la chaise. Il est moelleux, tout plié. Il est doux, maman. Oui. Glisse les bras. Nino glisse un bras, puis l'autre. Les manches sont chaudes. Il boutonne le devant, tout seul. Bravo, Nino. Tu as mis le pyjama. Le soir, on met le pyjama. Puis le dodo ? Puis le dodo. Viens dans la chambre. Le couloir est un peu sombre. Une petite lampe veille au bout. Papa ouvre le lit. L'oreiller est frais, bien blanc. Viens te coucher, Nino. Le corps a besoin de dormir. Nino pose la tête. La couverture sent le propre. Tu veux une petite histoire ? Oui, papa. Une toute courte. Papa raconte un petit bateau. Le bateau glisse sur l'eau calme. Il va où, le bateau ? Vers la rive. Tout doucement. Nino écoute. Ses yeux deviennent lourds. Je baisse la lumière. C'est l'heure du dodo. Ce n'est pas une punition. C'est le dodo. Le soir, on se couche. Pyjama, puis dodo. Oui. Bravo. Nino ferme les yeux. Il respire doucement. Le nuage du miroir s'efface déjà.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1339,8 +1339,10 @@
 narrateur|Nino vit ici, avec papa et maman.
 narrateur|En ce moment, l'eau du bain est encore tiède.
 maman|Tu as fini le bain, Nino ?
-enfant-m|Oui, maman. L'eau est douce.
-maman|Viens. Le pyjama t'attend.
+enfant-m|Oui, maman.
+enfant-m|L'eau est douce.
+maman|Viens.
+maman|Le pyjama t'attend.
 narrateur|Maman tend une serviette épaisse.
 narrateur|La serviette sent le linge chaud.
 narrateur|Nino se sèche près du tapis.
@@ -1355,7 +1357,8 @@
 maman|Bravo, Nino. Tu as mis le pyjama.
 maman|Le soir, on met le pyjama.
 enfant-m|Puis le dodo ?
-maman|Puis le dodo. Viens dans la chambre.
+maman|Puis le dodo.
+maman|Viens dans la chambre.
 narrateur|Le couloir est un peu sombre.
 narrateur|Une petite lampe veille au bout.
 narrateur|Papa ouvre le lit.
@@ -1375,15 +1378,15 @@
 maman|Je baisse la lumière.
 maman|C'est l'heure du dodo.
 papa|Ce n'est pas une punition.
-papa|C'est le dodo. Le soir, on se couche.
+papa|C'est le dodo.
+papa|Le soir, on se couche.
 enfant-m|Pyjama, puis dodo.
-papa|Oui. Bravo. Tu as fait du bon travail.
+papa|Oui. Bravo.
 narrateur|Nino ferme les yeux.
 narrateur|Il respire doucement.
 narrateur|Le nuage du miroir s'efface déjà.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1413,7 +1416,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Quentin va dormir. Que met-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino va dormir. Que met-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1568,7 +1571,6 @@
 narrateur|Que met-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1593,12 +1595,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a mis le pyjama. Il s'est couché. Tu as mis le pyjama, Nino ? Oui, papa. Le bleu. Bravo. Le soir, c'est le dodo. Tu as fait du bon travail. La chambre sent encore le savon, un peu.</t>
+          <t>Nino a mis le pyjama. Il s'est couché. Tu as mis le pyjama, Nino ? Oui, papa. Le bleu. Bravo. Le soir, c'est le dodo. La chambre sent encore le savon, un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Quentin a mis le pyjama. Il s'est couché. Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt;, c'est le dodo.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a mis le pyjama. Il s'est couché. Tu as mis le pyjama, Nino ? Oui, papa. Le bleu. Bravo. Le soir, c'est le dodo. La chambre sent encore le savon, un peu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1742,11 +1744,9 @@
 papa|Tu as mis le pyjama, Nino ?
 enfant-m|Oui, papa. Le bleu.
 papa|Bravo. Le soir, c'est le dodo.
-maman|Tu as fait du bon travail.
 narrateur|La chambre sent encore le savon, un peu.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Quentin respire doucement. Papa reste un moment.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa pose le livre du bateau. Tu as encore soif ? Un peu d'eau. Maman tend le verre. Nino boit une gorgée. L'eau est fraîche. On reste un moment, tout calme. Nino respire. Le pyjama est chaud. La goutte sur le carreau a séché.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1919,7 +1919,6 @@
 narrateur|La goutte sur le carreau a séché.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1944,12 +1943,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai mis le pyjama. On a fait le dodo. Bravo, Nino. Le soir, pyjama, puis dodo. L'histoire est finie.</t>
+          <t>J'ai mis le pyjama. On a fait le dodo. Bravo, Nino. Le soir, pyjama, puis dodo.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai mis le pyjama. On a fait le dodo. Bravo, Nino. Le soir, pyjama, puis dodo.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2087,11 +2086,9 @@
           <t>enfant-m|J'ai mis le pyjama.
 enfant-m|On a fait le dodo.
 papa|Bravo, Nino.
-maman|Le soir, pyjama, puis dodo.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Le soir, pyjama, puis dodo.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2110,7 +2107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2155,6 +2152,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-04.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Quentin, papa, maman</t>
+          <t>Nino, papa, maman</t>
         </is>
       </c>
     </row>
